--- a/Comag_Pub/Data.xlsx
+++ b/Comag_Pub/Data.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MATLAB_Git\MATLAB-atomic-calculation\Comag_Pub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625B2BBC-31D9-488D-A1BB-954BD0BA40C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF020A0-9DC7-4DC5-9CB1-B5B540D9EBC3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12015" activeTab="1" xr2:uid="{784CA7D4-7557-47FC-A711-2F72E730D1BC}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12015" activeTab="4" xr2:uid="{784CA7D4-7557-47FC-A711-2F72E730D1BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig. 1c" sheetId="1" r:id="rId1"/>
     <sheet name="Fig. 2b" sheetId="2" r:id="rId2"/>
+    <sheet name="Fig. 2d" sheetId="3" r:id="rId3"/>
+    <sheet name="Fig. 3a" sheetId="4" r:id="rId4"/>
+    <sheet name="Fig. 3b" sheetId="5" r:id="rId5"/>
+    <sheet name="Fig. 4" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>Precession time - 10 s (ms)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -49,6 +53,46 @@
   </si>
   <si>
     <t>s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>errorbar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B_x (mG)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B_y (mG)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lattice beam power (W)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Density ratio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x-error</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y-error</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Precession (ms)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S_z</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -101,11 +145,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -821,12 +868,3637 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FB4534-213B-42E0-BD51-8B855B2F7B65}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>0.187826086956522</v>
+      </c>
+      <c r="B2" s="1">
+        <v>-0.39512195121951199</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.72616099999999995</v>
+      </c>
+      <c r="D2" s="2">
+        <v>7.8102496758920893E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>0.28173913043478299</v>
+      </c>
+      <c r="B3" s="1">
+        <v>-0.39512195121951199</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.72615953103448305</v>
+      </c>
+      <c r="D3" s="2">
+        <v>9.3425649379349892E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>0.37565217391304401</v>
+      </c>
+      <c r="B4" s="1">
+        <v>-0.39512195121951199</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.72616611764705896</v>
+      </c>
+      <c r="D4" s="2">
+        <v>6.8999774333778696E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>0.46956521739130402</v>
+      </c>
+      <c r="B5" s="1">
+        <v>-0.39512195121951199</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.72615988235294104</v>
+      </c>
+      <c r="D5" s="2">
+        <v>6.8999774333778696E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>9.3913043478260905E-2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>-0.65853658536585402</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.72612787058823502</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1.6617346171145199E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>0.187826086956522</v>
+      </c>
+      <c r="B7" s="1">
+        <v>-0.65853658536585402</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.72610907058823504</v>
+      </c>
+      <c r="D7" s="2">
+        <v>9.4530271967823805E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>0.28173913043478299</v>
+      </c>
+      <c r="B8" s="1">
+        <v>-0.65853658536585402</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.72611499999999995</v>
+      </c>
+      <c r="D8" s="2">
+        <v>9.2195444572967904E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>0.28173913043478299</v>
+      </c>
+      <c r="B9" s="1">
+        <v>-0.92195121951219505</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.7260875</v>
+      </c>
+      <c r="D9" s="2">
+        <v>8.3216584885265407E-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>0.46956521739130402</v>
+      </c>
+      <c r="B10" s="1">
+        <v>-0.92195121951219505</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.72607268852458995</v>
+      </c>
+      <c r="D10" s="2">
+        <v>7.0071181223597803E-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>0.657391304347826</v>
+      </c>
+      <c r="B11" s="1">
+        <v>-0.92195121951219505</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.72609334117647095</v>
+      </c>
+      <c r="D11" s="2">
+        <v>8.4290156304387006E-6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>0.75130434782608702</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-0.92195121951219505</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.72611588000000005</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1.0614405306014599E-5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>9.3913043478260905E-2</v>
+      </c>
+      <c r="B13" s="1">
+        <v>-1.0536585365853699</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.72610549999999996</v>
+      </c>
+      <c r="D13" s="2">
+        <v>4.2720018726544201E-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>0.28173913043478299</v>
+      </c>
+      <c r="B14" s="1">
+        <v>-1.0536585365853699</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.72608649999999997</v>
+      </c>
+      <c r="D14" s="2">
+        <v>5.3150729063604904E-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>0.37565217391304401</v>
+      </c>
+      <c r="B15" s="1">
+        <v>-1.0536585365853699</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.72608024390243897</v>
+      </c>
+      <c r="D15" s="2">
+        <v>8.9681835662752E-6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>0.46956521739130402</v>
+      </c>
+      <c r="B16" s="1">
+        <v>-1.0536585365853699</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.72607517073170702</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4.6533619581276399E-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>0.56347826086956498</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-1.0536585365853699</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.72607851219512198</v>
+      </c>
+      <c r="D17" s="2">
+        <v>6.2278757730494398E-6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>0.657391304347826</v>
+      </c>
+      <c r="B18" s="1">
+        <v>-1.0536585365853699</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.72608512195121999</v>
+      </c>
+      <c r="D18" s="2">
+        <v>5.8941687676096902E-6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>9.3913043478260905E-2</v>
+      </c>
+      <c r="B19" s="1">
+        <v>-1.1853658536585401</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.72610093243243301</v>
+      </c>
+      <c r="D19" s="2">
+        <v>9.1346253655896207E-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>0.28173913043478299</v>
+      </c>
+      <c r="B20" s="1">
+        <v>-1.1853658536585401</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.7260875</v>
+      </c>
+      <c r="D20" s="2">
+        <v>4.2720018726544201E-6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>0.46956521739130402</v>
+      </c>
+      <c r="B21" s="1">
+        <v>-1.1853658536585401</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.72608953658536601</v>
+      </c>
+      <c r="D21" s="2">
+        <v>8.13333268321533E-6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>0.657391304347826</v>
+      </c>
+      <c r="B22" s="1">
+        <v>-1.1853658536585401</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.72610149999999996</v>
+      </c>
+      <c r="D22" s="2">
+        <v>6.9462219947196701E-6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>9.3913043478260905E-2</v>
+      </c>
+      <c r="B23" s="1">
+        <v>-1.44878048780488</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.72612231081081102</v>
+      </c>
+      <c r="D23" s="2">
+        <v>6.2209881801249002E-6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>0.28173913043478299</v>
+      </c>
+      <c r="B24" s="1">
+        <v>-1.44878048780488</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.72611550000000002</v>
+      </c>
+      <c r="D24" s="2">
+        <v>4.0311288741510596E-6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>0.46956521739130402</v>
+      </c>
+      <c r="B25" s="1">
+        <v>-1.44878048780488</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.72612783999999997</v>
+      </c>
+      <c r="D25" s="2">
+        <v>4.4513368778570397E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2645F994-DE2E-41E0-A6C0-F4243730B6B0}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.375" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>0.58695652173913104</v>
+      </c>
+      <c r="B2" s="1">
+        <v>-1.6463414634146301</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.72601249999999995</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3.0413812651514702E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>0.58695652173913104</v>
+      </c>
+      <c r="B3" s="1">
+        <v>-1.8109756097561001</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.72604900000000006</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4.9999999999587897E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>0.58695652173913104</v>
+      </c>
+      <c r="B4" s="1">
+        <v>-1.9756097560975601</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.72605299999999995</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4.2426406871410299E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>0.58695652173913104</v>
+      </c>
+      <c r="B5" s="1">
+        <v>-2.3048780487804899</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.72603147999999995</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4.7759396981047696E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>0.58695652173913104</v>
+      </c>
+      <c r="B6" s="1">
+        <v>-2.4695121951219501</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.72598180000000001</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4.1569219381743801E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>0.82173913043478297</v>
+      </c>
+      <c r="B7" s="1">
+        <v>-1.6463414634146301</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.72601450000000001</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4.2720018726544201E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>0.82173913043478297</v>
+      </c>
+      <c r="B8" s="1">
+        <v>-1.8109756097561001</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.72607003999999997</v>
+      </c>
+      <c r="D8" s="2">
+        <v>7.5285058278816801E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>0.82173913043478297</v>
+      </c>
+      <c r="B9" s="1">
+        <v>-1.9756097560975601</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.72608779999999995</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1.01823376490953E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>0.82173913043478297</v>
+      </c>
+      <c r="B10" s="1">
+        <v>-2.3048780487804899</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.72606099999999996</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3.6055512754651001E-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>0.82173913043478297</v>
+      </c>
+      <c r="B11" s="1">
+        <v>-2.4695121951219501</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.72602449999999996</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4.0311288741510596E-6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>0.84521739130434803</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-2.0414634146341499</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.72607423076923105</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4.7741909689495301E-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>1.05652173913044</v>
+      </c>
+      <c r="B13" s="1">
+        <v>-1.6463414634146301</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.726006268292683</v>
+      </c>
+      <c r="D13" s="2">
+        <v>5.5831820206082499E-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>1.05652173913044</v>
+      </c>
+      <c r="B14" s="1">
+        <v>-1.8109756097561001</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.72604599999999997</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3.1622776601599199E-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>1.05652173913044</v>
+      </c>
+      <c r="B15" s="1">
+        <v>-1.9756097560975601</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.7260605</v>
+      </c>
+      <c r="D15" s="2">
+        <v>3.9051248379638103E-6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>1.05652173913044</v>
+      </c>
+      <c r="B16" s="1">
+        <v>-2.3048780487804899</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.72605284000000003</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4.4513368778225604E-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>1.05652173913044</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-2.4695121951219501</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.726024</v>
+      </c>
+      <c r="D17" s="2">
+        <v>5.6568542494952097E-6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>1.2913043478260899</v>
+      </c>
+      <c r="B18" s="1">
+        <v>-1.9756097560975601</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.72602350000000004</v>
+      </c>
+      <c r="D18" s="2">
+        <v>8.4999999999943706E-6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>1.2913043478260899</v>
+      </c>
+      <c r="B19" s="1">
+        <v>-2.1402439024390199</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.72601938461538496</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2.5279502653994401E-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>1.2913043478260899</v>
+      </c>
+      <c r="B20" s="1">
+        <v>-2.3048780487804899</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.72598949999999995</v>
+      </c>
+      <c r="D20" s="2">
+        <v>6.2649820430634804E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C07E055B-7C05-40A5-9FA4-E478671D3EA9}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>30</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.72607900000000003</v>
+      </c>
+      <c r="C2" s="2">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.726074</v>
+      </c>
+      <c r="C3" s="2">
+        <v>3.9999999999999998E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.726078</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3.9999999999999998E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.72607699999999997</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3.9999999999999998E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.72607900000000003</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3.9999999999999998E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A895AD44-C404-42B6-8B14-94871458F249}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>0.27319758716231801</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.207698418629228</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.7260723</v>
+      </c>
+      <c r="D2" s="2">
+        <v>7.2400000000000001E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="B3" s="1">
+        <v>7.6489832294524301E-2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.726074</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>0.71153846153846201</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.11801046513024301</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.72607500000000003</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3.0000000000000001E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>1.0444444444444401</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.128531741116029</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.72606999999999999</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1.9999999999999999E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>1.63636363636364</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.275977515953018</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.726074</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3.0000000000000001E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62747EBC-16B3-42CA-B975-1881CF897D94}">
+  <dimension ref="A1:C252"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.875" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.829175045892797</v>
+      </c>
+      <c r="C2" s="1">
+        <v>7.1747612031437993E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.56375271051778897</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4.5884425297502598E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.20104255766122101</v>
+      </c>
+      <c r="C4" s="1">
+        <v>3.7509527888498401E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1">
+        <v>-0.23252159109960499</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3.1120331667582098E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>40</v>
+      </c>
+      <c r="B6" s="1">
+        <v>-0.44567682855797303</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.7610092677285302E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>50</v>
+      </c>
+      <c r="B7" s="1">
+        <v>-0.53022498771703896</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1.1507457294512901E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>60</v>
+      </c>
+      <c r="B8" s="1">
+        <v>-0.63572755848347295</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3.9160299663109901E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>70</v>
+      </c>
+      <c r="B9" s="1">
+        <v>-0.56526667783128404</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6.42007072129991E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>80</v>
+      </c>
+      <c r="B10" s="1">
+        <v>-0.47622390774394802</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3.0227177424327598E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>90</v>
+      </c>
+      <c r="B11" s="1">
+        <v>-0.23892366323808301</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1.40774492039817E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>100</v>
+      </c>
+      <c r="B12" s="1">
+        <v>6.3261269491815902E-2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3.9666026871242099E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>110</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.26381477598062297</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.12181109438218E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>120</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.31325198599208098</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1.3525316575409599E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>130</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.38748854095707203</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1.37670538554695E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>140</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.40116847769740799</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3.1115868336201599E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>150</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.29237387581907598</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.1698603625586399E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>160</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.11401105756883601</v>
+      </c>
+      <c r="C18" s="1">
+        <v>3.50781881758018E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>170</v>
+      </c>
+      <c r="B19" s="1">
+        <v>-1.4046531532071299E-2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5.1282016211033803E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>180</v>
+      </c>
+      <c r="B20" s="1">
+        <v>-0.215873961126227</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1.9141358513324599E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>190</v>
+      </c>
+      <c r="B21" s="1">
+        <v>-0.36865027478265699</v>
+      </c>
+      <c r="C21" s="1">
+        <v>4.1945991667350503E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>200</v>
+      </c>
+      <c r="B22" s="1">
+        <v>-0.52827128619519004</v>
+      </c>
+      <c r="C22" s="1">
+        <v>4.1707946727718798E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>210</v>
+      </c>
+      <c r="B23" s="1">
+        <v>-0.63726127302226998</v>
+      </c>
+      <c r="C23" s="1">
+        <v>6.0359237526744602E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>220</v>
+      </c>
+      <c r="B24" s="1">
+        <v>-0.52876480439124596</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3.8818677468544602E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>230</v>
+      </c>
+      <c r="B25" s="1">
+        <v>-0.43528707469352601</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1.1831173406167199E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>240</v>
+      </c>
+      <c r="B26" s="1">
+        <v>-0.307780375981351</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1.01334212286884E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>250</v>
+      </c>
+      <c r="B27" s="1">
+        <v>-0.26388155648917999</v>
+      </c>
+      <c r="C27" s="1">
+        <v>6.5941038995458306E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>260</v>
+      </c>
+      <c r="B28" s="1">
+        <v>-0.20240849195485</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1.71441796196274E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>270</v>
+      </c>
+      <c r="B29" s="1">
+        <v>-3.8206294960498301E-2</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.91371877949539E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>280</v>
+      </c>
+      <c r="B30" s="1">
+        <v>2.31186662301738E-2</v>
+      </c>
+      <c r="C30" s="1">
+        <v>8.34146057618162E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>290</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0.152849013539189</v>
+      </c>
+      <c r="C31" s="1">
+        <v>3.2313267308565798E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>300</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0.27790571136365699</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.1118613015006098E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>310</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0.394599300030957</v>
+      </c>
+      <c r="C33" s="1">
+        <v>6.6277109027044999E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>320</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.49428531002799903</v>
+      </c>
+      <c r="C34" s="1">
+        <v>5.65060417064795E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>330</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.50851333443982405</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.3219310077786701E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>340</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0.53437833129494305</v>
+      </c>
+      <c r="C36" s="1">
+        <v>3.9143138595102898E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>350</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0.42927507990000302</v>
+      </c>
+      <c r="C37" s="1">
+        <v>3.1696145271568402E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>360</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.38187897636173901</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3.5038437672657102E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>370</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.38029968623736699</v>
+      </c>
+      <c r="C39" s="1">
+        <v>8.74098383822665E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>380</v>
+      </c>
+      <c r="B40" s="1">
+        <v>0.299460429256939</v>
+      </c>
+      <c r="C40" s="1">
+        <v>4.3030182846603999E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>390</v>
+      </c>
+      <c r="B41" s="1">
+        <v>0.279329206298357</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3.3256802026912502E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>400</v>
+      </c>
+      <c r="B42" s="1">
+        <v>0.30745778451573202</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3.8501641351610001E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>410</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0.17442715084150301</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.7447541412549001E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>420</v>
+      </c>
+      <c r="B44" s="1">
+        <v>0.15602247914457901</v>
+      </c>
+      <c r="C44" s="1">
+        <v>4.2785083747229502E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>430</v>
+      </c>
+      <c r="B45" s="1">
+        <v>3.7885131493870398E-2</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1.19597108796756E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>440</v>
+      </c>
+      <c r="B46" s="1">
+        <v>-5.86582040713318E-2</v>
+      </c>
+      <c r="C46" s="1">
+        <v>8.1741196443608194E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>450</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1.7172405491927799E-2</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2.8260818861639201E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>460</v>
+      </c>
+      <c r="B48" s="1">
+        <v>0.131282198855809</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2.0371176434423498E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>470</v>
+      </c>
+      <c r="B49" s="1">
+        <v>0.14215389979788401</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2.7941161848397299E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>480</v>
+      </c>
+      <c r="B50" s="1">
+        <v>0.14810097815952999</v>
+      </c>
+      <c r="C50" s="1">
+        <v>4.5906782042940401E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>490</v>
+      </c>
+      <c r="B51" s="1">
+        <v>0.16392625430458499</v>
+      </c>
+      <c r="C51" s="1">
+        <v>3.5031525551914702E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>500</v>
+      </c>
+      <c r="B52" s="1">
+        <v>0.14951503200899699</v>
+      </c>
+      <c r="C52" s="1">
+        <v>3.4614353877550699E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>510</v>
+      </c>
+      <c r="B53" s="1">
+        <v>0.18335006985647601</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1.4823656207180401E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>520</v>
+      </c>
+      <c r="B54" s="1">
+        <v>0.14867556939520599</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1.29952962832819E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>530</v>
+      </c>
+      <c r="B55" s="1">
+        <v>0.16686461463579499</v>
+      </c>
+      <c r="C55" s="1">
+        <v>3.8300452687653898E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>540</v>
+      </c>
+      <c r="B56" s="1">
+        <v>4.9338224908815002E-2</v>
+      </c>
+      <c r="C56" s="1">
+        <v>3.3624503133321798E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>550</v>
+      </c>
+      <c r="B57" s="1">
+        <v>4.5793005708107203E-2</v>
+      </c>
+      <c r="C57" s="1">
+        <v>3.1722199975594001E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>560</v>
+      </c>
+      <c r="B58" s="1">
+        <v>-7.8881141309157202E-2</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1.93649122470342E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>570</v>
+      </c>
+      <c r="B59" s="1">
+        <v>-7.07501598862392E-2</v>
+      </c>
+      <c r="C59" s="1">
+        <v>6.6636284190198401E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>580</v>
+      </c>
+      <c r="B60" s="1">
+        <v>-0.12754087921573401</v>
+      </c>
+      <c r="C60" s="1">
+        <v>4.0835733255899197E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>590</v>
+      </c>
+      <c r="B61" s="1">
+        <v>-0.19882273976957099</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1.5934039318590699E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>600</v>
+      </c>
+      <c r="B62" s="1">
+        <v>-0.26955721872427202</v>
+      </c>
+      <c r="C62" s="1">
+        <v>2.6008274557475598E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>610</v>
+      </c>
+      <c r="B63" s="1">
+        <v>-0.39166288833381502</v>
+      </c>
+      <c r="C63" s="1">
+        <v>2.80448929563905E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>620</v>
+      </c>
+      <c r="B64" s="1">
+        <v>-0.45088119031067803</v>
+      </c>
+      <c r="C64" s="1">
+        <v>4.0570666480496197E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>630</v>
+      </c>
+      <c r="B65" s="1">
+        <v>-0.54096524253682698</v>
+      </c>
+      <c r="C65" s="1">
+        <v>4.7106287750873298E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>640</v>
+      </c>
+      <c r="B66" s="1">
+        <v>-0.50192195442989196</v>
+      </c>
+      <c r="C66" s="1">
+        <v>7.3525114670107306E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>650</v>
+      </c>
+      <c r="B67" s="1">
+        <v>-0.44572968354382703</v>
+      </c>
+      <c r="C67" s="1">
+        <v>9.0253266846650904E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>660</v>
+      </c>
+      <c r="B68" s="1">
+        <v>-0.36816542011064901</v>
+      </c>
+      <c r="C68" s="1">
+        <v>2.0503702402025301E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>670</v>
+      </c>
+      <c r="B69" s="1">
+        <v>-0.131725193266193</v>
+      </c>
+      <c r="C69" s="1">
+        <v>6.8693180323105105E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>680</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2.5585164061302301E-2</v>
+      </c>
+      <c r="C70" s="1">
+        <v>1.9320816640941402E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>690</v>
+      </c>
+      <c r="B71" s="1">
+        <v>0.24350968571741199</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1.7927713783873901E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>700</v>
+      </c>
+      <c r="B72" s="1">
+        <v>0.42569084660474099</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1.14330968516431E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>710</v>
+      </c>
+      <c r="B73" s="1">
+        <v>0.49730345793827402</v>
+      </c>
+      <c r="C73" s="1">
+        <v>4.0480910751570898E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>720</v>
+      </c>
+      <c r="B74" s="1">
+        <v>0.59097668984930596</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1.87434836469943E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>730</v>
+      </c>
+      <c r="B75" s="1">
+        <v>0.60974263199666401</v>
+      </c>
+      <c r="C75" s="1">
+        <v>1.14788040432212E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>740</v>
+      </c>
+      <c r="B76" s="1">
+        <v>0.62107324709011702</v>
+      </c>
+      <c r="C76" s="1">
+        <v>2.5915169935481399E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>750</v>
+      </c>
+      <c r="B77" s="1">
+        <v>0.48858161395627703</v>
+      </c>
+      <c r="C77" s="1">
+        <v>4.2229991818329697E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>760</v>
+      </c>
+      <c r="B78" s="1">
+        <v>0.224356395279003</v>
+      </c>
+      <c r="C78" s="1">
+        <v>4.8075079365500997E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>770</v>
+      </c>
+      <c r="B79" s="1">
+        <v>-0.13416740650032699</v>
+      </c>
+      <c r="C79" s="1">
+        <v>1.58548176606725E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>780</v>
+      </c>
+      <c r="B80" s="1">
+        <v>-0.31956128605447198</v>
+      </c>
+      <c r="C80" s="1">
+        <v>3.1691789059244697E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>790</v>
+      </c>
+      <c r="B81" s="1">
+        <v>-0.34778278879754498</v>
+      </c>
+      <c r="C81" s="1">
+        <v>2.9889322254379101E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>800</v>
+      </c>
+      <c r="B82" s="1">
+        <v>-0.37588730807556497</v>
+      </c>
+      <c r="C82" s="1">
+        <v>5.7279446478228101E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>810</v>
+      </c>
+      <c r="B83" s="1">
+        <v>-0.26281145991535698</v>
+      </c>
+      <c r="C83" s="1">
+        <v>6.1292780948669599E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>820</v>
+      </c>
+      <c r="B84" s="1">
+        <v>-0.23670235379329099</v>
+      </c>
+      <c r="C84" s="1">
+        <v>4.74530462199068E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>830</v>
+      </c>
+      <c r="B85" s="2">
+        <v>2.72688736740976E-5</v>
+      </c>
+      <c r="C85" s="1">
+        <v>6.89892682653198E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>840</v>
+      </c>
+      <c r="B86" s="1">
+        <v>0.363457165967633</v>
+      </c>
+      <c r="C86" s="1">
+        <v>2.33609729605989E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>850</v>
+      </c>
+      <c r="B87" s="1">
+        <v>0.53602633002329003</v>
+      </c>
+      <c r="C87" s="1">
+        <v>3.0525481076447199E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>860</v>
+      </c>
+      <c r="B88" s="1">
+        <v>0.70565035277791899</v>
+      </c>
+      <c r="C88" s="1">
+        <v>3.7177901087039701E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>870</v>
+      </c>
+      <c r="B89" s="1">
+        <v>0.75089585066936404</v>
+      </c>
+      <c r="C89" s="1">
+        <v>3.36807679138501E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>880</v>
+      </c>
+      <c r="B90" s="1">
+        <v>0.78135592827324696</v>
+      </c>
+      <c r="C90" s="1">
+        <v>2.04774612012706E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>890</v>
+      </c>
+      <c r="B91" s="1">
+        <v>0.73285718767787</v>
+      </c>
+      <c r="C91" s="1">
+        <v>2.2664205754766902E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>900</v>
+      </c>
+      <c r="B92" s="1">
+        <v>0.60439906146286104</v>
+      </c>
+      <c r="C92" s="1">
+        <v>4.2723301103173697E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>910</v>
+      </c>
+      <c r="B93" s="1">
+        <v>0.35598972902533199</v>
+      </c>
+      <c r="C93" s="1">
+        <v>3.01604600713282E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>920</v>
+      </c>
+      <c r="B94" s="1">
+        <v>-7.0214897456746694E-2</v>
+      </c>
+      <c r="C94" s="1">
+        <v>2.0843697768733301E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>930</v>
+      </c>
+      <c r="B95" s="1">
+        <v>-0.404720171300402</v>
+      </c>
+      <c r="C95" s="1">
+        <v>4.7341369292780197E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>940</v>
+      </c>
+      <c r="B96" s="1">
+        <v>-0.62714434437203004</v>
+      </c>
+      <c r="C96" s="1">
+        <v>7.0880347248853601E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>950</v>
+      </c>
+      <c r="B97" s="1">
+        <v>-0.72500913806675604</v>
+      </c>
+      <c r="C97" s="1">
+        <v>3.1593068381604299E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>960</v>
+      </c>
+      <c r="B98" s="1">
+        <v>-0.69137795230552501</v>
+      </c>
+      <c r="C98" s="1">
+        <v>6.0434323358566799E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>970</v>
+      </c>
+      <c r="B99" s="1">
+        <v>-0.73041148609470496</v>
+      </c>
+      <c r="C99" s="1">
+        <v>7.6195993668581902E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>980</v>
+      </c>
+      <c r="B100" s="1">
+        <v>-0.59553269603432202</v>
+      </c>
+      <c r="C100" s="1">
+        <v>2.5766729257606799E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>990</v>
+      </c>
+      <c r="B101" s="1">
+        <v>-0.45633889153788998</v>
+      </c>
+      <c r="C101" s="1">
+        <v>4.6217914806104703E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B102" s="1">
+        <v>-0.123643251619989</v>
+      </c>
+      <c r="C102" s="1">
+        <v>5.1243222309293797E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>1010</v>
+      </c>
+      <c r="B103" s="1">
+        <v>5.0638475469841099E-2</v>
+      </c>
+      <c r="C103" s="1">
+        <v>5.4068010450131002E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>1020</v>
+      </c>
+      <c r="B104" s="1">
+        <v>0.170514022678942</v>
+      </c>
+      <c r="C104" s="1">
+        <v>2.7849898948751398E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>1030</v>
+      </c>
+      <c r="B105" s="1">
+        <v>0.25774927025649702</v>
+      </c>
+      <c r="C105" s="1">
+        <v>6.7231860757990702E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>1040</v>
+      </c>
+      <c r="B106" s="1">
+        <v>0.22099926224434799</v>
+      </c>
+      <c r="C106" s="1">
+        <v>3.2980652117120597E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>1050</v>
+      </c>
+      <c r="B107" s="1">
+        <v>0.231352457657442</v>
+      </c>
+      <c r="C107" s="1">
+        <v>3.45393188162516E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>1060</v>
+      </c>
+      <c r="B108" s="1">
+        <v>0.16895260681101201</v>
+      </c>
+      <c r="C108" s="1">
+        <v>6.1930290479138402E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>1070</v>
+      </c>
+      <c r="B109" s="1">
+        <v>0.27917216247844701</v>
+      </c>
+      <c r="C109" s="1">
+        <v>7.1585406122082695E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>1080</v>
+      </c>
+      <c r="B110" s="1">
+        <v>9.1086931164029605E-2</v>
+      </c>
+      <c r="C110" s="1">
+        <v>5.2771163707062002E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>1090</v>
+      </c>
+      <c r="B111" s="1">
+        <v>-2.57310044271741E-2</v>
+      </c>
+      <c r="C111" s="1">
+        <v>5.0572810088084098E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>1100</v>
+      </c>
+      <c r="B112" s="1">
+        <v>-0.11696621167669299</v>
+      </c>
+      <c r="C112" s="1">
+        <v>6.3060378411125301E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
+        <v>1110</v>
+      </c>
+      <c r="B113" s="1">
+        <v>-0.19345614644783199</v>
+      </c>
+      <c r="C113" s="1">
+        <v>7.6059662187960703E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
+        <v>1120</v>
+      </c>
+      <c r="B114" s="1">
+        <v>-0.170487923527642</v>
+      </c>
+      <c r="C114" s="1">
+        <v>6.7390744003903699E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
+        <v>1130</v>
+      </c>
+      <c r="B115" s="1">
+        <v>-0.110595931327323</v>
+      </c>
+      <c r="C115" s="1">
+        <v>9.9046940456986907E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
+        <v>1140</v>
+      </c>
+      <c r="B116" s="1">
+        <v>-0.104346478674033</v>
+      </c>
+      <c r="C116" s="1">
+        <v>4.6353187073519903E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
+        <v>1150</v>
+      </c>
+      <c r="B117" s="1">
+        <v>-6.4092055619123595E-2</v>
+      </c>
+      <c r="C117" s="1">
+        <v>7.8519540063140797E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
+        <v>1160</v>
+      </c>
+      <c r="B118" s="1">
+        <v>7.0587781831370098E-3</v>
+      </c>
+      <c r="C118" s="1">
+        <v>7.5511154057270102E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
+        <v>1170</v>
+      </c>
+      <c r="B119" s="1">
+        <v>0.11072877487414701</v>
+      </c>
+      <c r="C119" s="1">
+        <v>3.8876280122887803E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
+        <v>1180</v>
+      </c>
+      <c r="B120" s="1">
+        <v>0.30453646282307401</v>
+      </c>
+      <c r="C120" s="1">
+        <v>5.4003060312033502E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
+        <v>1190</v>
+      </c>
+      <c r="B121" s="1">
+        <v>0.357587653555961</v>
+      </c>
+      <c r="C121" s="1">
+        <v>1.0968718952393999E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
+        <v>1200</v>
+      </c>
+      <c r="B122" s="1">
+        <v>0.34969593283737999</v>
+      </c>
+      <c r="C122" s="1">
+        <v>1.45775007796496E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
+        <v>1210</v>
+      </c>
+      <c r="B123" s="1">
+        <v>0.43606477362443402</v>
+      </c>
+      <c r="C123" s="1">
+        <v>5.0630076066025098E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
+        <v>1220</v>
+      </c>
+      <c r="B124" s="1">
+        <v>0.52380954770467403</v>
+      </c>
+      <c r="C124" s="1">
+        <v>2.6777734590722701E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>1230</v>
+      </c>
+      <c r="B125" s="1">
+        <v>0.54860733649811599</v>
+      </c>
+      <c r="C125" s="1">
+        <v>9.6823048898713501E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>1240</v>
+      </c>
+      <c r="B126" s="1">
+        <v>0.49623618484834803</v>
+      </c>
+      <c r="C126" s="1">
+        <v>5.08043273128998E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>1250</v>
+      </c>
+      <c r="B127" s="1">
+        <v>0.49771069947595997</v>
+      </c>
+      <c r="C127" s="1">
+        <v>5.9945327445033898E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>1260</v>
+      </c>
+      <c r="B128" s="1">
+        <v>0.38554134153893899</v>
+      </c>
+      <c r="C128" s="1">
+        <v>4.0148458383385301E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>1270</v>
+      </c>
+      <c r="B129" s="1">
+        <v>0.24706830843602601</v>
+      </c>
+      <c r="C129" s="1">
+        <v>4.0820333202133503E-3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>1280</v>
+      </c>
+      <c r="B130" s="1">
+        <v>0.20188768101725099</v>
+      </c>
+      <c r="C130" s="1">
+        <v>5.5841350182749501E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>1290</v>
+      </c>
+      <c r="B131" s="1">
+        <v>3.2581416184420099E-2</v>
+      </c>
+      <c r="C131" s="1">
+        <v>4.5422735982023198E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>1300</v>
+      </c>
+      <c r="B132" s="1">
+        <v>-5.8566479337635299E-2</v>
+      </c>
+      <c r="C132" s="1">
+        <v>2.1162084284200199E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>1310</v>
+      </c>
+      <c r="B133" s="1">
+        <v>-0.16053362878903399</v>
+      </c>
+      <c r="C133" s="1">
+        <v>6.8978372059633794E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>1320</v>
+      </c>
+      <c r="B134" s="1">
+        <v>-0.213721179589589</v>
+      </c>
+      <c r="C134" s="1">
+        <v>2.56816087798666E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>1330</v>
+      </c>
+      <c r="B135" s="1">
+        <v>-0.20676674486781799</v>
+      </c>
+      <c r="C135" s="1">
+        <v>8.2882333803033698E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>1340</v>
+      </c>
+      <c r="B136" s="1">
+        <v>-0.16320260669734399</v>
+      </c>
+      <c r="C136" s="1">
+        <v>8.0568885680019894E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>1350</v>
+      </c>
+      <c r="B137" s="1">
+        <v>-0.12747552486272201</v>
+      </c>
+      <c r="C137" s="1">
+        <v>8.2799736028752499E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>1360</v>
+      </c>
+      <c r="B138" s="1">
+        <v>-0.13908720491085799</v>
+      </c>
+      <c r="C138" s="1">
+        <v>7.0573184247581106E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>1370</v>
+      </c>
+      <c r="B139" s="1">
+        <v>-8.3688223716098104E-2</v>
+      </c>
+      <c r="C139" s="1">
+        <v>0.14011499147612599</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>1380</v>
+      </c>
+      <c r="B140" s="1">
+        <v>-2.4409680644506999E-2</v>
+      </c>
+      <c r="C140" s="1">
+        <v>5.8472725863488999E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>1390</v>
+      </c>
+      <c r="B141" s="1">
+        <v>-0.12792848794383499</v>
+      </c>
+      <c r="C141" s="1">
+        <v>6.5158008047589394E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>1400</v>
+      </c>
+      <c r="B142" s="1">
+        <v>-5.0650242454729197E-2</v>
+      </c>
+      <c r="C142" s="1">
+        <v>4.4868640385725599E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>1410</v>
+      </c>
+      <c r="B143" s="1">
+        <v>-2.59781699327023E-2</v>
+      </c>
+      <c r="C143" s="1">
+        <v>4.8573638400082698E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>1420</v>
+      </c>
+      <c r="B144" s="1">
+        <v>2.73022168037905E-2</v>
+      </c>
+      <c r="C144" s="1">
+        <v>4.0097345704437799E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>1430</v>
+      </c>
+      <c r="B145" s="1">
+        <v>3.1934500616917799E-2</v>
+      </c>
+      <c r="C145" s="1">
+        <v>4.9460721488166201E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>1440</v>
+      </c>
+      <c r="B146" s="1">
+        <v>-5.5874408717035903E-2</v>
+      </c>
+      <c r="C146" s="1">
+        <v>7.4187313275900502E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>1450</v>
+      </c>
+      <c r="B147" s="1">
+        <v>-3.1366920474240501E-2</v>
+      </c>
+      <c r="C147" s="1">
+        <v>0.10968687668645501</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>1460</v>
+      </c>
+      <c r="B148" s="1">
+        <v>-1.3525566433182199E-2</v>
+      </c>
+      <c r="C148" s="1">
+        <v>5.2722867740310798E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>1470</v>
+      </c>
+      <c r="B149" s="1">
+        <v>9.0746351317212107E-2</v>
+      </c>
+      <c r="C149" s="1">
+        <v>2.87857791197976E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>1480</v>
+      </c>
+      <c r="B150" s="1">
+        <v>0.10847282561546701</v>
+      </c>
+      <c r="C150" s="1">
+        <v>8.4594703453388501E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>1490</v>
+      </c>
+      <c r="B151" s="1">
+        <v>0.12401486776385399</v>
+      </c>
+      <c r="C151" s="1">
+        <v>0.18783115888752699</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>1500</v>
+      </c>
+      <c r="B152" s="1">
+        <v>3.9754369141348798E-2</v>
+      </c>
+      <c r="C152" s="1">
+        <v>0.15088191307368701</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
+        <v>1510</v>
+      </c>
+      <c r="B153" s="1">
+        <v>-0.22136328811931799</v>
+      </c>
+      <c r="C153" s="1">
+        <v>0.10256775584372201</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
+        <v>1520</v>
+      </c>
+      <c r="B154" s="1">
+        <v>-0.25090832234796701</v>
+      </c>
+      <c r="C154" s="1">
+        <v>0.148811582360276</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
+        <v>1530</v>
+      </c>
+      <c r="B155" s="1">
+        <v>-0.32623724868850301</v>
+      </c>
+      <c r="C155" s="1">
+        <v>8.72294076671839E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
+        <v>1540</v>
+      </c>
+      <c r="B156" s="1">
+        <v>-0.305321442575124</v>
+      </c>
+      <c r="C156" s="1">
+        <v>5.6393721003026698E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
+        <v>1550</v>
+      </c>
+      <c r="B157" s="1">
+        <v>-0.211919821482733</v>
+      </c>
+      <c r="C157" s="1">
+        <v>3.1943512504546898E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
+        <v>1560</v>
+      </c>
+      <c r="B158" s="1">
+        <v>-0.159349566480253</v>
+      </c>
+      <c r="C158" s="1">
+        <v>1.6684657897904499E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
+        <v>1570</v>
+      </c>
+      <c r="B159" s="1">
+        <v>4.3549572450922502E-2</v>
+      </c>
+      <c r="C159" s="1">
+        <v>1.53378589271562E-2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
+        <v>1580</v>
+      </c>
+      <c r="B160" s="1">
+        <v>0.23288384839305101</v>
+      </c>
+      <c r="C160" s="1">
+        <v>6.3658977796325497E-2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
+        <v>1590</v>
+      </c>
+      <c r="B161" s="1">
+        <v>0.39402559374470902</v>
+      </c>
+      <c r="C161" s="1">
+        <v>4.6344427542214503E-2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
+        <v>1600</v>
+      </c>
+      <c r="B162" s="1">
+        <v>0.608386260393602</v>
+      </c>
+      <c r="C162" s="1">
+        <v>4.4018684136088303E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A163" s="1">
+        <v>1610</v>
+      </c>
+      <c r="B163" s="1">
+        <v>0.67602796969081402</v>
+      </c>
+      <c r="C163" s="1">
+        <v>4.7403753646723702E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A164" s="1">
+        <v>1620</v>
+      </c>
+      <c r="B164" s="1">
+        <v>0.68887307434934797</v>
+      </c>
+      <c r="C164" s="1">
+        <v>3.1186614798003699E-2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A165" s="1">
+        <v>1630</v>
+      </c>
+      <c r="B165" s="1">
+        <v>0.68464942799792805</v>
+      </c>
+      <c r="C165" s="1">
+        <v>3.8603463424225597E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A166" s="1">
+        <v>1640</v>
+      </c>
+      <c r="B166" s="1">
+        <v>0.65408389881957296</v>
+      </c>
+      <c r="C166" s="1">
+        <v>2.62983171434478E-2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A167" s="1">
+        <v>1650</v>
+      </c>
+      <c r="B167" s="1">
+        <v>0.51462889713103599</v>
+      </c>
+      <c r="C167" s="1">
+        <v>5.7197442626085303E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A168" s="1">
+        <v>1660</v>
+      </c>
+      <c r="B168" s="1">
+        <v>0.32317437072397498</v>
+      </c>
+      <c r="C168" s="1">
+        <v>2.5276296730795199E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A169" s="1">
+        <v>1670</v>
+      </c>
+      <c r="B169" s="1">
+        <v>-3.7208627565347097E-2</v>
+      </c>
+      <c r="C169" s="1">
+        <v>3.4022167378868998E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A170" s="1">
+        <v>1680</v>
+      </c>
+      <c r="B170" s="1">
+        <v>-0.33155069845142698</v>
+      </c>
+      <c r="C170" s="1">
+        <v>3.5389911437885703E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A171" s="1">
+        <v>1690</v>
+      </c>
+      <c r="B171" s="1">
+        <v>-0.41211973543207697</v>
+      </c>
+      <c r="C171" s="1">
+        <v>5.73373642458746E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A172" s="1">
+        <v>1700</v>
+      </c>
+      <c r="B172" s="1">
+        <v>-0.42772923394345702</v>
+      </c>
+      <c r="C172" s="1">
+        <v>6.1904134175120702E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A173" s="1">
+        <v>1710</v>
+      </c>
+      <c r="B173" s="1">
+        <v>-0.33469961670597798</v>
+      </c>
+      <c r="C173" s="1">
+        <v>6.7107157410616097E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A174" s="1">
+        <v>1720</v>
+      </c>
+      <c r="B174" s="1">
+        <v>-0.31556314756222897</v>
+      </c>
+      <c r="C174" s="1">
+        <v>7.4904237438617197E-2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A175" s="1">
+        <v>1730</v>
+      </c>
+      <c r="B175" s="1">
+        <v>-0.102019733644601</v>
+      </c>
+      <c r="C175" s="1">
+        <v>9.8499859325844596E-2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A176" s="1">
+        <v>1740</v>
+      </c>
+      <c r="B176" s="1">
+        <v>0.16202623160369101</v>
+      </c>
+      <c r="C176" s="1">
+        <v>0.133181206010685</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A177" s="1">
+        <v>1750</v>
+      </c>
+      <c r="B177" s="1">
+        <v>0.37384475555072</v>
+      </c>
+      <c r="C177" s="1">
+        <v>7.5402332660728294E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A178" s="1">
+        <v>1760</v>
+      </c>
+      <c r="B178" s="1">
+        <v>0.54057190175731695</v>
+      </c>
+      <c r="C178" s="1">
+        <v>3.5871462528558502E-2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A179" s="1">
+        <v>1770</v>
+      </c>
+      <c r="B179" s="1">
+        <v>0.57612687515096594</v>
+      </c>
+      <c r="C179" s="1">
+        <v>6.5160077875759101E-2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A180" s="1">
+        <v>1780</v>
+      </c>
+      <c r="B180" s="1">
+        <v>0.56813189022925703</v>
+      </c>
+      <c r="C180" s="1">
+        <v>3.5196780623160701E-2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A181" s="1">
+        <v>1790</v>
+      </c>
+      <c r="B181" s="1">
+        <v>0.47518158535834298</v>
+      </c>
+      <c r="C181" s="1">
+        <v>3.4746551150401102E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A182" s="1">
+        <v>1800</v>
+      </c>
+      <c r="B182" s="1">
+        <v>0.33605838588235298</v>
+      </c>
+      <c r="C182" s="1">
+        <v>1.6131176738039401E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A183" s="1">
+        <v>1810</v>
+      </c>
+      <c r="B183" s="1">
+        <v>6.2974043335028096E-2</v>
+      </c>
+      <c r="C183" s="1">
+        <v>1.3683824288935401E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A184" s="1">
+        <v>1820</v>
+      </c>
+      <c r="B184" s="1">
+        <v>-0.189368192717526</v>
+      </c>
+      <c r="C184" s="1">
+        <v>8.3038210433908494E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A185" s="1">
+        <v>1830</v>
+      </c>
+      <c r="B185" s="1">
+        <v>-0.38252254523406698</v>
+      </c>
+      <c r="C185" s="1">
+        <v>3.2717267871086003E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A186" s="1">
+        <v>1840</v>
+      </c>
+      <c r="B186" s="1">
+        <v>-0.59963505359694802</v>
+      </c>
+      <c r="C186" s="1">
+        <v>1.1966010696009499E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A187" s="1">
+        <v>1850</v>
+      </c>
+      <c r="B187" s="1">
+        <v>-0.652701530603501</v>
+      </c>
+      <c r="C187" s="1">
+        <v>6.8984330548366501E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A188" s="1">
+        <v>1860</v>
+      </c>
+      <c r="B188" s="1">
+        <v>-0.71325589743854301</v>
+      </c>
+      <c r="C188" s="1">
+        <v>3.6152841022902601E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A189" s="1">
+        <v>1870</v>
+      </c>
+      <c r="B189" s="1">
+        <v>-0.62501027049188296</v>
+      </c>
+      <c r="C189" s="1">
+        <v>1.4701652673095899E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A190" s="1">
+        <v>1880</v>
+      </c>
+      <c r="B190" s="1">
+        <v>-0.46286362952454702</v>
+      </c>
+      <c r="C190" s="1">
+        <v>3.6647110952363997E-2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A191" s="1">
+        <v>1890</v>
+      </c>
+      <c r="B191" s="1">
+        <v>-0.288265410759316</v>
+      </c>
+      <c r="C191" s="1">
+        <v>2.3662588498998001E-2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A192" s="1">
+        <v>1900</v>
+      </c>
+      <c r="B192" s="1">
+        <v>-8.9561474631269206E-2</v>
+      </c>
+      <c r="C192" s="1">
+        <v>3.7510214464737499E-2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A193" s="1">
+        <v>1910</v>
+      </c>
+      <c r="B193" s="1">
+        <v>2.5035845916345102E-2</v>
+      </c>
+      <c r="C193" s="1">
+        <v>5.7888033522097801E-2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A194" s="1">
+        <v>1920</v>
+      </c>
+      <c r="B194" s="1">
+        <v>0.17888936205630901</v>
+      </c>
+      <c r="C194" s="1">
+        <v>4.1627127358633803E-2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A195" s="1">
+        <v>1930</v>
+      </c>
+      <c r="B195" s="1">
+        <v>0.31754216128679502</v>
+      </c>
+      <c r="C195" s="1">
+        <v>6.6854846435554394E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A196" s="1">
+        <v>1940</v>
+      </c>
+      <c r="B196" s="1">
+        <v>0.37521154491537001</v>
+      </c>
+      <c r="C196" s="1">
+        <v>7.1242598219486697E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A197" s="1">
+        <v>1950</v>
+      </c>
+      <c r="B197" s="1">
+        <v>0.41109241301757399</v>
+      </c>
+      <c r="C197" s="1">
+        <v>3.0485507185122999E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A198" s="1">
+        <v>1960</v>
+      </c>
+      <c r="B198" s="1">
+        <v>0.45193221728670502</v>
+      </c>
+      <c r="C198" s="1">
+        <v>7.2209109778505698E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A199" s="1">
+        <v>1970</v>
+      </c>
+      <c r="B199" s="1">
+        <v>0.44288291736548402</v>
+      </c>
+      <c r="C199" s="1">
+        <v>2.7245666249199298E-2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A200" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B200" s="1">
+        <v>0.32539907247930999</v>
+      </c>
+      <c r="C200" s="1">
+        <v>8.8215844353770306E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A201" s="1">
+        <v>1990</v>
+      </c>
+      <c r="B201" s="1">
+        <v>0.231132960286139</v>
+      </c>
+      <c r="C201" s="1">
+        <v>8.5431561138397893E-2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A202" s="1">
+        <v>2000</v>
+      </c>
+      <c r="B202" s="1">
+        <v>4.6432235881636003E-2</v>
+      </c>
+      <c r="C202" s="1">
+        <v>0.11285361289346101</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A203" s="1">
+        <v>2010</v>
+      </c>
+      <c r="B203" s="1">
+        <v>2.6927320323207301E-3</v>
+      </c>
+      <c r="C203" s="1">
+        <v>6.8782565422275704E-2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A204" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B204" s="1">
+        <v>-3.4533474788385303E-2</v>
+      </c>
+      <c r="C204" s="1">
+        <v>9.2873447164398201E-2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A205" s="1">
+        <v>2030</v>
+      </c>
+      <c r="B205" s="1">
+        <v>-2.39442081387207E-2</v>
+      </c>
+      <c r="C205" s="1">
+        <v>3.6646200385102398E-2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A206" s="1">
+        <v>2040</v>
+      </c>
+      <c r="B206" s="1">
+        <v>-6.9157917464725702E-2</v>
+      </c>
+      <c r="C206" s="1">
+        <v>2.1905567945364801E-2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A207" s="1">
+        <v>2050</v>
+      </c>
+      <c r="B207" s="1">
+        <v>-8.8050674007244006E-2</v>
+      </c>
+      <c r="C207" s="1">
+        <v>2.1921367610363798E-2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A208" s="1">
+        <v>2060</v>
+      </c>
+      <c r="B208" s="1">
+        <v>-4.2930557927562001E-2</v>
+      </c>
+      <c r="C208" s="1">
+        <v>6.6442685026829207E-2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A209" s="1">
+        <v>2070</v>
+      </c>
+      <c r="B209" s="1">
+        <v>8.0947128104558397E-2</v>
+      </c>
+      <c r="C209" s="1">
+        <v>5.0290372121217397E-2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A210" s="1">
+        <v>2080</v>
+      </c>
+      <c r="B210" s="1">
+        <v>0.23571351287388601</v>
+      </c>
+      <c r="C210" s="1">
+        <v>5.3644643233231898E-2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A211" s="1">
+        <v>2090</v>
+      </c>
+      <c r="B211" s="1">
+        <v>0.31633751482512501</v>
+      </c>
+      <c r="C211" s="1">
+        <v>4.1119527580287002E-2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A212" s="1">
+        <v>2100</v>
+      </c>
+      <c r="B212" s="1">
+        <v>0.351018823728381</v>
+      </c>
+      <c r="C212" s="1">
+        <v>8.7924473719767193E-2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A213" s="1">
+        <v>2110</v>
+      </c>
+      <c r="B213" s="1">
+        <v>0.38955012039921399</v>
+      </c>
+      <c r="C213" s="1">
+        <v>5.9689936594551997E-2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A214" s="1">
+        <v>2120</v>
+      </c>
+      <c r="B214" s="1">
+        <v>0.491545127875126</v>
+      </c>
+      <c r="C214" s="1">
+        <v>0.114298632516294</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A215" s="1">
+        <v>2130</v>
+      </c>
+      <c r="B215" s="1">
+        <v>0.48509339681348501</v>
+      </c>
+      <c r="C215" s="1">
+        <v>3.8219324305547697E-2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A216" s="1">
+        <v>2140</v>
+      </c>
+      <c r="B216" s="1">
+        <v>0.40829055505839601</v>
+      </c>
+      <c r="C216" s="1">
+        <v>2.3296183733271199E-2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A217" s="1">
+        <v>2150</v>
+      </c>
+      <c r="B217" s="1">
+        <v>0.27810238863876202</v>
+      </c>
+      <c r="C217" s="1">
+        <v>3.6998890711102003E-2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A218" s="1">
+        <v>2160</v>
+      </c>
+      <c r="B218" s="1">
+        <v>0.164515614653168</v>
+      </c>
+      <c r="C218" s="1">
+        <v>7.8698332441143395E-3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A219" s="1">
+        <v>2170</v>
+      </c>
+      <c r="B219" s="1">
+        <v>-1.4628628776910501E-2</v>
+      </c>
+      <c r="C219" s="1">
+        <v>8.5172951255232093E-3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A220" s="1">
+        <v>2180</v>
+      </c>
+      <c r="B220" s="1">
+        <v>-0.12475589253837401</v>
+      </c>
+      <c r="C220" s="1">
+        <v>6.7915440282527301E-2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A221" s="1">
+        <v>2190</v>
+      </c>
+      <c r="B221" s="1">
+        <v>-0.10447022283419</v>
+      </c>
+      <c r="C221" s="1">
+        <v>2.9241786341865E-2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A222" s="1">
+        <v>2200</v>
+      </c>
+      <c r="B222" s="1">
+        <v>-0.256511620147514</v>
+      </c>
+      <c r="C222" s="1">
+        <v>2.8892851608154298E-2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A223" s="1">
+        <v>2210</v>
+      </c>
+      <c r="B223" s="1">
+        <v>-0.29131361555803598</v>
+      </c>
+      <c r="C223" s="1">
+        <v>3.73037585193721E-2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A224" s="1">
+        <v>2220</v>
+      </c>
+      <c r="B224" s="1">
+        <v>-0.310060565897604</v>
+      </c>
+      <c r="C224" s="1">
+        <v>3.7139362623382403E-2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A225" s="1">
+        <v>2230</v>
+      </c>
+      <c r="B225" s="1">
+        <v>-0.29653569764636201</v>
+      </c>
+      <c r="C225" s="1">
+        <v>5.4427278366939599E-2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A226" s="1">
+        <v>2240</v>
+      </c>
+      <c r="B226" s="1">
+        <v>-0.15335487099796699</v>
+      </c>
+      <c r="C226" s="1">
+        <v>5.8502042256290902E-2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A227" s="1">
+        <v>2250</v>
+      </c>
+      <c r="B227" s="1">
+        <v>-0.12734139334112199</v>
+      </c>
+      <c r="C227" s="1">
+        <v>4.5573392133285498E-2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A228" s="1">
+        <v>2260</v>
+      </c>
+      <c r="B228" s="1">
+        <v>-0.125844700320596</v>
+      </c>
+      <c r="C228" s="1">
+        <v>3.0765889976348802E-2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A229" s="1">
+        <v>2270</v>
+      </c>
+      <c r="B229" s="1">
+        <v>-0.101618977585529</v>
+      </c>
+      <c r="C229" s="1">
+        <v>4.3475516019117103E-2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A230" s="1">
+        <v>2280</v>
+      </c>
+      <c r="B230" s="1">
+        <v>-0.10946267476281001</v>
+      </c>
+      <c r="C230" s="1">
+        <v>3.2411023276793099E-2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A231" s="1">
+        <v>2290</v>
+      </c>
+      <c r="B231" s="1">
+        <v>-3.3975068001879799E-2</v>
+      </c>
+      <c r="C231" s="1">
+        <v>6.9547372657201706E-2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A232" s="1">
+        <v>2300</v>
+      </c>
+      <c r="B232" s="1">
+        <v>-0.101497586964576</v>
+      </c>
+      <c r="C232" s="1">
+        <v>9.6215322166611203E-2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A233" s="1">
+        <v>2310</v>
+      </c>
+      <c r="B233" s="1">
+        <v>-3.3128885158813501E-2</v>
+      </c>
+      <c r="C233" s="1">
+        <v>5.3296952823353103E-2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A234" s="1">
+        <v>2320</v>
+      </c>
+      <c r="B234" s="1">
+        <v>-5.5820232942919001E-3</v>
+      </c>
+      <c r="C234" s="1">
+        <v>9.6437653497263895E-2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A235" s="1">
+        <v>2330</v>
+      </c>
+      <c r="B235" s="1">
+        <v>-3.4571477055452798E-2</v>
+      </c>
+      <c r="C235" s="1">
+        <v>7.7370209342581805E-2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A236" s="1">
+        <v>2340</v>
+      </c>
+      <c r="B236" s="1">
+        <v>1.57489301325517E-2</v>
+      </c>
+      <c r="C236" s="1">
+        <v>0.125430939420761</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A237" s="1">
+        <v>2350</v>
+      </c>
+      <c r="B237" s="1">
+        <v>0.116496341392754</v>
+      </c>
+      <c r="C237" s="1">
+        <v>8.2704576410814704E-2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A238" s="1">
+        <v>2360</v>
+      </c>
+      <c r="B238" s="1">
+        <v>0.23369776769640399</v>
+      </c>
+      <c r="C238" s="1">
+        <v>5.7405130322308102E-2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A239" s="1">
+        <v>2370</v>
+      </c>
+      <c r="B239" s="1">
+        <v>0.30175972415944502</v>
+      </c>
+      <c r="C239" s="1">
+        <v>6.0760327517987003E-2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A240" s="1">
+        <v>2380</v>
+      </c>
+      <c r="B240" s="1">
+        <v>0.36230285261152501</v>
+      </c>
+      <c r="C240" s="1">
+        <v>6.69223358295232E-2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A241" s="1">
+        <v>2390</v>
+      </c>
+      <c r="B241" s="1">
+        <v>0.24501470289893301</v>
+      </c>
+      <c r="C241" s="1">
+        <v>0.107891658920804</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A242" s="1">
+        <v>2400</v>
+      </c>
+      <c r="B242" s="1">
+        <v>0.14267477565988301</v>
+      </c>
+      <c r="C242" s="1">
+        <v>0.14439427515365</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A243" s="1">
+        <v>2410</v>
+      </c>
+      <c r="B243" s="1">
+        <v>5.9583756107683003E-2</v>
+      </c>
+      <c r="C243" s="1">
+        <v>0.10240118712926199</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A244" s="1">
+        <v>2420</v>
+      </c>
+      <c r="B244" s="1">
+        <v>-0.14683604885825799</v>
+      </c>
+      <c r="C244" s="1">
+        <v>6.7833417777339894E-2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A245" s="1">
+        <v>2430</v>
+      </c>
+      <c r="B245" s="1">
+        <v>-0.131213843382263</v>
+      </c>
+      <c r="C245" s="1">
+        <v>6.0721970312189399E-2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A246" s="1">
+        <v>2440</v>
+      </c>
+      <c r="B246" s="1">
+        <v>-0.24249190020254799</v>
+      </c>
+      <c r="C246" s="1">
+        <v>2.2167673574203999E-2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A247" s="1">
+        <v>2450</v>
+      </c>
+      <c r="B247" s="1">
+        <v>-0.122071302989063</v>
+      </c>
+      <c r="C247" s="1">
+        <v>3.2940560298256198E-2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A248" s="1">
+        <v>2460</v>
+      </c>
+      <c r="B248" s="1">
+        <v>-6.1888606520872198E-2</v>
+      </c>
+      <c r="C248" s="1">
+        <v>0.10980263653235001</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A249" s="1">
+        <v>2470</v>
+      </c>
+      <c r="B249" s="1">
+        <v>5.4651852514427099E-2</v>
+      </c>
+      <c r="C249" s="1">
+        <v>0.13645711601640101</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A250" s="1">
+        <v>2480</v>
+      </c>
+      <c r="B250" s="1">
+        <v>0.315915087091032</v>
+      </c>
+      <c r="C250" s="1">
+        <v>6.0599498182218402E-2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A251" s="1">
+        <v>2490</v>
+      </c>
+      <c r="B251" s="1">
+        <v>0.39313433925936903</v>
+      </c>
+      <c r="C251" s="1">
+        <v>0.106083769742677</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A252" s="1">
+        <v>2500</v>
+      </c>
+      <c r="B252" s="1">
+        <v>0.59239546614180605</v>
+      </c>
+      <c r="C252" s="1">
+        <v>3.4252597157824E-2</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
